--- a/survey_templates/032_esd_safety_equipment_survey--survey_templates.xlsx
+++ b/survey_templates/032_esd_safety_equipment_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'control_1',_'value':_'control_1'}</t>
+          <t>control_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Control 1', 'value': 'Control 1'}</t>
+          <t>Control 1</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'control_2',_'value':_'control_2'}</t>
+          <t>control_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Control 2', 'value': 'Control 2'}</t>
+          <t>Control 2</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'control_3',_'value':_'control_3'}</t>
+          <t>control_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Control 3', 'value': 'Control 3'}</t>
+          <t>Control 3</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'self',_'value':_'self'}</t>
+          <t>self</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Self', 'value': 'Self'}</t>
+          <t>Self</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'self',_'value':_'self'}</t>
+          <t>self</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Self', 'value': 'Self'}</t>
+          <t>Self</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'another',_'value':_'another'}</t>
+          <t>another</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Another', 'value': 'Another'}</t>
+          <t>Another</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
